--- a/data/trans_orig/P39C-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P39C-Edad-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última vez que le midieron la glucosa en 2016</t>
+          <t>Población según el tiempo transcurrido desde la última vez que le midieron la glucosa en 2016 (tasa de respuesta: 97,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23029</t>
+          <t>21350</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44657</t>
+          <t>43596</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15109</t>
+          <t>14987</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32278</t>
+          <t>33389</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41343</t>
+          <t>43168</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69949</t>
+          <t>70494</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,35%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68409</t>
+          <t>69703</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>97201</t>
+          <t>97813</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74034</t>
+          <t>73950</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>103786</t>
+          <t>104641</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>152246</t>
+          <t>153121</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>192280</t>
+          <t>190682</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,53%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40094</t>
+          <t>40233</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66331</t>
+          <t>64923</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>57119</t>
+          <t>56789</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>84926</t>
+          <t>84993</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>103878</t>
+          <t>102923</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>141711</t>
+          <t>141873</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,9%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12003</t>
+          <t>11540</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29341</t>
+          <t>29905</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14382</t>
+          <t>14480</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31226</t>
+          <t>31427</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29582</t>
+          <t>30339</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52879</t>
+          <t>54143</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19510</t>
+          <t>20297</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39788</t>
+          <t>40713</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30575</t>
+          <t>30115</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>54350</t>
+          <t>53207</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>54311</t>
+          <t>55818</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>86026</t>
+          <t>84722</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56778</t>
+          <t>57913</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>89727</t>
+          <t>88750</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37916</t>
+          <t>37332</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62851</t>
+          <t>61950</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>101732</t>
+          <t>101580</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>141204</t>
+          <t>142254</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>115877</t>
+          <t>115073</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>151833</t>
+          <t>152731</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>123593</t>
+          <t>124797</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163980</t>
+          <t>164741</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>250414</t>
+          <t>250607</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>305146</t>
+          <t>304608</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>89846</t>
+          <t>91107</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>125001</t>
+          <t>125383</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>123532</t>
+          <t>123954</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>161740</t>
+          <t>161292</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>224375</t>
+          <t>225014</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>276843</t>
+          <t>277440</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18603</t>
+          <t>17523</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38243</t>
+          <t>37756</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34882</t>
+          <t>34922</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61534</t>
+          <t>60253</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58108</t>
+          <t>58890</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>92204</t>
+          <t>91440</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26708</t>
+          <t>26889</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51851</t>
+          <t>49454</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56222</t>
+          <t>56373</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>87318</t>
+          <t>86237</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>90497</t>
+          <t>89814</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>127355</t>
+          <t>128749</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57023</t>
+          <t>57176</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89084</t>
+          <t>88844</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>62395</t>
+          <t>63272</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>94409</t>
+          <t>95654</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>126598</t>
+          <t>130824</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>173238</t>
+          <t>175037</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>145955</t>
+          <t>144113</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>188986</t>
+          <t>187931</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>136705</t>
+          <t>137106</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>178419</t>
+          <t>179280</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>292745</t>
+          <t>294009</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>353202</t>
+          <t>352719</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,25%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>141154</t>
+          <t>139941</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>184899</t>
+          <t>182650</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>135044</t>
+          <t>135369</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>177089</t>
+          <t>176488</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>287112</t>
+          <t>286524</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>343949</t>
+          <t>346716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,68%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39826</t>
+          <t>42166</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71144</t>
+          <t>71488</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48015</t>
+          <t>49489</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>75696</t>
+          <t>78890</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>98857</t>
+          <t>98412</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>139987</t>
+          <t>138651</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>47728</t>
+          <t>48955</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>78659</t>
+          <t>80935</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>75723</t>
+          <t>75017</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>109787</t>
+          <t>108767</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>133124</t>
+          <t>132049</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>180065</t>
+          <t>180717</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58998</t>
+          <t>58371</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>90728</t>
+          <t>90345</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46127</t>
+          <t>48827</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>76565</t>
+          <t>78166</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>112222</t>
+          <t>113637</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>160500</t>
+          <t>157810</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>123212</t>
+          <t>123458</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>166440</t>
+          <t>165371</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>149950</t>
+          <t>152362</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>196138</t>
+          <t>198657</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>286210</t>
+          <t>286541</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>348110</t>
+          <t>347432</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,57%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>133346</t>
+          <t>134237</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>177919</t>
+          <t>175964</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>142593</t>
+          <t>143691</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>187718</t>
+          <t>187230</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>288754</t>
+          <t>287569</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>351896</t>
+          <t>348522</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,67%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53642</t>
+          <t>52865</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>86658</t>
+          <t>86076</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>62980</t>
+          <t>63464</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>96878</t>
+          <t>95998</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>122689</t>
+          <t>124584</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>170823</t>
+          <t>169823</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,43%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>75215</t>
+          <t>76014</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>112083</t>
+          <t>112635</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>73779</t>
+          <t>73981</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>109477</t>
+          <t>107193</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>158261</t>
+          <t>158201</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>207119</t>
+          <t>208325</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>31758</t>
+          <t>30967</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>57370</t>
+          <t>56768</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>15503</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>36472</t>
+          <t>36422</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>51517</t>
+          <t>51619</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>85938</t>
+          <t>86460</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>84665</t>
+          <t>83079</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>121685</t>
+          <t>122018</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>88204</t>
+          <t>88038</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>126130</t>
+          <t>125532</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>182993</t>
+          <t>182923</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>235827</t>
+          <t>235329</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,57%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>108012</t>
+          <t>107761</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>147674</t>
+          <t>147150</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>115132</t>
+          <t>115610</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>156033</t>
+          <t>156952</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>233444</t>
+          <t>234961</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>291535</t>
+          <t>291434</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,9%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>57302</t>
+          <t>57900</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>90139</t>
+          <t>91624</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>60392</t>
+          <t>58873</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>92791</t>
+          <t>92899</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>125607</t>
+          <t>125446</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>170761</t>
+          <t>172487</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>71989</t>
+          <t>72414</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>107056</t>
+          <t>107815</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>94021</t>
+          <t>92786</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>133557</t>
+          <t>130225</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>176902</t>
+          <t>176904</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>228929</t>
+          <t>228981</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>22274</t>
+          <t>22300</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>16790</t>
+          <t>17051</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>13962</t>
+          <t>13710</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>34588</t>
+          <t>33413</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>53585</t>
+          <t>53161</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>82444</t>
+          <t>83784</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>40416</t>
+          <t>38757</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>67312</t>
+          <t>65929</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>99264</t>
+          <t>101515</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>137873</t>
+          <t>142083</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>78013</t>
+          <t>77966</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>108697</t>
+          <t>112005</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>107953</t>
+          <t>110619</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>146049</t>
+          <t>147289</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>197223</t>
+          <t>197327</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>244587</t>
+          <t>246987</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>36,12%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>46505</t>
+          <t>48719</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>76137</t>
+          <t>78739</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>60903</t>
+          <t>58775</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>91714</t>
+          <t>92385</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>113409</t>
+          <t>115748</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>155988</t>
+          <t>157913</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>69582</t>
+          <t>68892</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>100855</t>
+          <t>101307</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>83069</t>
+          <t>83362</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>118087</t>
+          <t>117773</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>161809</t>
+          <t>164324</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>211193</t>
+          <t>211176</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>3170</t>
+          <t>2516</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>11604</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>17412</t>
+          <t>15984</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>7997</t>
+          <t>8346</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>24437</t>
+          <t>25255</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>20756</t>
+          <t>20894</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>38412</t>
+          <t>37871</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>44803</t>
+          <t>44524</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>77116</t>
+          <t>74862</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>72064</t>
+          <t>70420</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>107786</t>
+          <t>107827</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>60907</t>
+          <t>60185</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>87327</t>
+          <t>87196</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>100669</t>
+          <t>101131</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>142530</t>
+          <t>141819</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>171760</t>
+          <t>171911</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>220517</t>
+          <t>221312</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,31%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>51341</t>
+          <t>51262</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>75423</t>
+          <t>75581</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>54660</t>
+          <t>53632</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>89430</t>
+          <t>89666</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>109974</t>
+          <t>111157</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>153444</t>
+          <t>156885</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>59524</t>
+          <t>59470</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>84888</t>
+          <t>85086</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>105383</t>
+          <t>102603</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>148146</t>
+          <t>146032</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>173595</t>
+          <t>173344</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>224606</t>
+          <t>220018</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,1%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>281520</t>
+          <t>279654</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>350513</t>
+          <t>348754</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>221858</t>
+          <t>221359</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>284715</t>
+          <t>283908</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>516579</t>
+          <t>521810</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>611179</t>
+          <t>612555</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>680673</t>
+          <t>680428</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>773417</t>
+          <t>773753</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>733677</t>
+          <t>732802</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>833040</t>
+          <t>830799</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1435423</t>
+          <t>1438837</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1571228</t>
+          <t>1572458</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>721375</t>
+          <t>720362</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>816625</t>
+          <t>815338</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>865630</t>
+          <t>865861</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>967719</t>
+          <t>964915</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1618075</t>
+          <t>1613853</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1758349</t>
+          <t>1752680</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,04%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>326974</t>
+          <t>330688</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>405139</t>
+          <t>404019</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>384799</t>
+          <t>389115</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>469729</t>
+          <t>470399</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>742969</t>
+          <t>740085</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>849474</t>
+          <t>846161</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>432525</t>
+          <t>432030</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>508543</t>
+          <t>510298</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>586564</t>
+          <t>585361</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>678512</t>
+          <t>677930</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1039868</t>
+          <t>1040577</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1163914</t>
+          <t>1165572</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última vez que le midieron la glucosa en 2023</t>
+          <t>Población según el tiempo transcurrido desde la última vez que le midieron la glucosa en 2023 (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18693</t>
+          <t>18570</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53967</t>
+          <t>52091</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17173</t>
+          <t>18090</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41278</t>
+          <t>43134</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42338</t>
+          <t>42752</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84521</t>
+          <t>86036</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,12%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42743</t>
+          <t>42982</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88411</t>
+          <t>90111</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29551</t>
+          <t>28770</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62541</t>
+          <t>60265</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>81531</t>
+          <t>79062</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>135534</t>
+          <t>136509</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,68%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36646</t>
+          <t>37518</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>82972</t>
+          <t>85258</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32179</t>
+          <t>31486</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60667</t>
+          <t>61651</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>79599</t>
+          <t>78072</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>135615</t>
+          <t>133946</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>35,99%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9726</t>
+          <t>9632</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43758</t>
+          <t>43812</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11229</t>
+          <t>10847</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33580</t>
+          <t>35088</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26239</t>
+          <t>26655</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67745</t>
+          <t>66433</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22375</t>
+          <t>21168</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32938</t>
+          <t>33987</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>66109</t>
+          <t>67220</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40628</t>
+          <t>40640</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>83018</t>
+          <t>80013</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>21,5%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21465</t>
+          <t>21363</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47054</t>
+          <t>49217</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27530</t>
+          <t>26488</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51942</t>
+          <t>52245</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54657</t>
+          <t>54218</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88821</t>
+          <t>89654</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>86219</t>
+          <t>85634</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>125746</t>
+          <t>125386</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>91211</t>
+          <t>90073</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>126486</t>
+          <t>127081</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>184942</t>
+          <t>186785</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>240754</t>
+          <t>240566</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,5%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>59643</t>
+          <t>59107</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>98263</t>
+          <t>97173</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>71942</t>
+          <t>73772</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>106065</t>
+          <t>107638</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>140360</t>
+          <t>142480</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>192227</t>
+          <t>191343</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17952</t>
+          <t>17800</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45570</t>
+          <t>44893</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31181</t>
+          <t>30958</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56590</t>
+          <t>55703</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53431</t>
+          <t>54254</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90429</t>
+          <t>89886</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,76%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16521</t>
+          <t>15930</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42047</t>
+          <t>41802</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>46197</t>
+          <t>46088</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77472</t>
+          <t>76555</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>70102</t>
+          <t>68593</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>110146</t>
+          <t>108368</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33663</t>
+          <t>33405</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60571</t>
+          <t>61262</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35517</t>
+          <t>35960</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57367</t>
+          <t>56785</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>74042</t>
+          <t>75361</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>108643</t>
+          <t>109350</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>103768</t>
+          <t>106192</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>143847</t>
+          <t>144260</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>120738</t>
+          <t>122714</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>153226</t>
+          <t>152766</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>235086</t>
+          <t>237030</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>288368</t>
+          <t>287914</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>108771</t>
+          <t>108582</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>148351</t>
+          <t>146771</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>114500</t>
+          <t>114378</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>145511</t>
+          <t>145912</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>229926</t>
+          <t>231373</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>282049</t>
+          <t>280693</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,25%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44408</t>
+          <t>46102</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74689</t>
+          <t>74715</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45057</t>
+          <t>45510</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67411</t>
+          <t>68722</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>96998</t>
+          <t>98842</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>133747</t>
+          <t>134636</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>45627</t>
+          <t>44469</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>75251</t>
+          <t>74634</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>75681</t>
+          <t>76378</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>101806</t>
+          <t>102619</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>127202</t>
+          <t>128432</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>166565</t>
+          <t>169116</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,43%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28133</t>
+          <t>28701</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55822</t>
+          <t>53082</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32957</t>
+          <t>32517</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53973</t>
+          <t>55134</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>66649</t>
+          <t>66900</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>100875</t>
+          <t>100996</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>125574</t>
+          <t>125615</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>165708</t>
+          <t>167858</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>137795</t>
+          <t>136315</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>187317</t>
+          <t>186852</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>278277</t>
+          <t>279174</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>340614</t>
+          <t>342200</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,8%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>153375</t>
+          <t>150874</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>195245</t>
+          <t>194090</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>185132</t>
+          <t>186740</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>285195</t>
+          <t>306086</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>356105</t>
+          <t>352998</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>479156</t>
+          <t>473788</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>39,88%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>56366</t>
+          <t>54944</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>86563</t>
+          <t>87059</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>69316</t>
+          <t>69034</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>101348</t>
+          <t>100393</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>135795</t>
+          <t>135018</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>179957</t>
+          <t>178563</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>96995</t>
+          <t>98200</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>135900</t>
+          <t>136379</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>108488</t>
+          <t>108150</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>148925</t>
+          <t>148801</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>216610</t>
+          <t>213876</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>273428</t>
+          <t>271231</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>33764</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>58498</t>
+          <t>59014</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>23035</t>
+          <t>22759</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>39552</t>
+          <t>38908</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>61834</t>
+          <t>62752</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>93384</t>
+          <t>93893</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>105187</t>
+          <t>106024</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>142560</t>
+          <t>143937</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>90175</t>
+          <t>90625</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>118006</t>
+          <t>118135</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>204502</t>
+          <t>206207</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>248863</t>
+          <t>251857</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,59%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>122312</t>
+          <t>122171</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>160488</t>
+          <t>157638</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>144322</t>
+          <t>143154</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>174340</t>
+          <t>173864</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>277420</t>
+          <t>277531</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>327034</t>
+          <t>323704</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,61%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>81165</t>
+          <t>81458</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>114227</t>
+          <t>114448</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>84947</t>
+          <t>84859</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>110460</t>
+          <t>110715</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>172637</t>
+          <t>174632</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>216642</t>
+          <t>214395</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>88224</t>
+          <t>90452</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>126056</t>
+          <t>126054</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>107818</t>
+          <t>108031</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>134926</t>
+          <t>135452</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>204341</t>
+          <t>205271</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>248470</t>
+          <t>249910</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,4%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>9982</t>
+          <t>9836</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>22655</t>
+          <t>22287</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4808</t>
+          <t>4860</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>25594</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>13347</t>
+          <t>13841</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>42380</t>
+          <t>42532</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>52440</t>
+          <t>53392</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>76279</t>
+          <t>77451</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>26089</t>
+          <t>29504</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>126124</t>
+          <t>126247</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>73843</t>
+          <t>69970</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>188618</t>
+          <t>189980</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>91254</t>
+          <t>90850</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>119096</t>
+          <t>118198</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>194237</t>
+          <t>194230</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>500840</t>
+          <t>497759</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>294813</t>
+          <t>293629</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>679584</t>
+          <t>705212</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>74,88%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>57992</t>
+          <t>58047</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>81401</t>
+          <t>82816</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>24654</t>
+          <t>25054</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>108420</t>
+          <t>108081</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>68469</t>
+          <t>66383</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>182415</t>
+          <t>181483</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,27%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>83168</t>
+          <t>82289</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>108728</t>
+          <t>109790</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>35899</t>
+          <t>34538</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>149556</t>
+          <t>152631</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>100132</t>
+          <t>86988</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>251489</t>
+          <t>251682</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,72%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>4753</t>
+          <t>4592</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>14893</t>
+          <t>14218</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>10459</t>
+          <t>9956</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>21801</t>
+          <t>21165</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>16993</t>
+          <t>16534</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>31846</t>
+          <t>31371</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -10627,12 +10627,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>32751</t>
+          <t>33909</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>52514</t>
+          <t>52736</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10642,12 +10642,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10662,12 +10662,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>50399</t>
+          <t>50298</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>70336</t>
+          <t>72056</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10677,12 +10677,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10697,12 +10697,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>89220</t>
+          <t>91008</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>116759</t>
+          <t>118232</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10712,12 +10712,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -10740,12 +10740,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>62348</t>
+          <t>64142</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>85938</t>
+          <t>85860</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10755,12 +10755,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10775,12 +10775,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>94841</t>
+          <t>96361</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>120152</t>
+          <t>121237</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10790,12 +10790,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>166279</t>
+          <t>165894</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>200367</t>
+          <t>201689</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10825,12 +10825,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,68%</t>
         </is>
       </c>
     </row>
@@ -10853,12 +10853,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>68878</t>
+          <t>66424</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>91879</t>
+          <t>90673</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10868,12 +10868,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10888,12 +10888,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>90003</t>
+          <t>89509</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>113096</t>
+          <t>113268</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10903,12 +10903,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10923,12 +10923,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>164206</t>
+          <t>163080</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>197524</t>
+          <t>196585</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10938,12 +10938,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,93%</t>
         </is>
       </c>
     </row>
@@ -10966,12 +10966,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>60314</t>
+          <t>61995</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>83405</t>
+          <t>85994</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10981,12 +10981,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11001,12 +11001,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>107524</t>
+          <t>105330</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>131578</t>
+          <t>130981</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11016,12 +11016,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11036,12 +11036,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>173973</t>
+          <t>172087</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>208185</t>
+          <t>207727</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11051,12 +11051,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,57%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>188895</t>
+          <t>189985</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>252832</t>
+          <t>253249</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>170455</t>
+          <t>169140</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>243935</t>
+          <t>245341</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>370556</t>
+          <t>376305</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>476555</t>
+          <t>477555</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -11309,12 +11309,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>619599</t>
+          <t>624114</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>716986</t>
+          <t>719194</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11324,12 +11324,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11344,12 +11344,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>539355</t>
+          <t>514877</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>763920</t>
+          <t>764924</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11359,12 +11359,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1198886</t>
+          <t>1198206</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1452057</t>
+          <t>1452035</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11394,7 +11394,7 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -11422,12 +11422,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>708105</t>
+          <t>709204</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>805649</t>
+          <t>807642</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -11437,12 +11437,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>923479</t>
+          <t>917760</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1571757</t>
+          <t>1561249</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1669950</t>
+          <t>1666576</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>2346436</t>
+          <t>2360790</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -11507,12 +11507,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,53%</t>
         </is>
       </c>
     </row>
@@ -11535,12 +11535,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>386905</t>
+          <t>388860</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>466108</t>
+          <t>465000</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -11550,12 +11550,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>360904</t>
+          <t>371900</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>519477</t>
+          <t>521615</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -11585,12 +11585,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>784907</t>
+          <t>794632</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>954601</t>
+          <t>966083</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -11620,12 +11620,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -11648,12 +11648,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>446863</t>
+          <t>443283</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>527397</t>
+          <t>522492</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -11663,12 +11663,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>499434</t>
+          <t>527623</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>724281</t>
+          <t>726740</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -11698,12 +11698,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -11718,12 +11718,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1021834</t>
+          <t>1002787</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1220016</t>
+          <t>1217733</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -11733,12 +11733,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,42%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P39C-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P39C-Edad-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21350</t>
+          <t>22648</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43596</t>
+          <t>44562</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14987</t>
+          <t>15248</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33389</t>
+          <t>33443</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43168</t>
+          <t>42242</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70494</t>
+          <t>71153</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69703</t>
+          <t>69598</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>97813</t>
+          <t>98673</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73950</t>
+          <t>74480</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>104641</t>
+          <t>102956</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>153121</t>
+          <t>150636</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>190682</t>
+          <t>191210</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,65%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40233</t>
+          <t>40019</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64923</t>
+          <t>66278</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>56789</t>
+          <t>58041</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>84993</t>
+          <t>84727</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>102923</t>
+          <t>103305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>141873</t>
+          <t>141502</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,82%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11540</t>
+          <t>11675</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29905</t>
+          <t>28032</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14480</t>
+          <t>13246</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31427</t>
+          <t>31095</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30339</t>
+          <t>29274</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54143</t>
+          <t>52239</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,38%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20297</t>
+          <t>19464</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40713</t>
+          <t>39997</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30115</t>
+          <t>29533</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>53207</t>
+          <t>54203</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>55818</t>
+          <t>56187</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>84722</t>
+          <t>85327</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,59%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57913</t>
+          <t>55688</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88750</t>
+          <t>87809</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37332</t>
+          <t>37833</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61950</t>
+          <t>63189</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>101580</t>
+          <t>101423</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>142254</t>
+          <t>144196</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,39%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>115073</t>
+          <t>118007</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>152731</t>
+          <t>154721</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>124797</t>
+          <t>122290</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>164741</t>
+          <t>161577</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>250607</t>
+          <t>249718</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>304608</t>
+          <t>303931</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,66%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>91107</t>
+          <t>89154</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>125383</t>
+          <t>124057</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>123954</t>
+          <t>123375</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>161292</t>
+          <t>161653</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>225014</t>
+          <t>221645</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>277440</t>
+          <t>273917</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,04%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17523</t>
+          <t>17891</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37756</t>
+          <t>38110</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34922</t>
+          <t>35292</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60253</t>
+          <t>60767</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58890</t>
+          <t>58180</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91440</t>
+          <t>92068</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26889</t>
+          <t>26795</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49454</t>
+          <t>50680</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56373</t>
+          <t>56986</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>86237</t>
+          <t>88792</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>89814</t>
+          <t>91011</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>128749</t>
+          <t>129608</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57176</t>
+          <t>56427</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>88844</t>
+          <t>90571</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63272</t>
+          <t>62992</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>95654</t>
+          <t>92518</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>130824</t>
+          <t>126923</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>175037</t>
+          <t>172422</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>144113</t>
+          <t>145002</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>187931</t>
+          <t>188236</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>137106</t>
+          <t>137930</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>179280</t>
+          <t>181172</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>294009</t>
+          <t>296179</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>352719</t>
+          <t>355835</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,54%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>139941</t>
+          <t>140467</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>182650</t>
+          <t>183953</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>135369</t>
+          <t>134243</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>176488</t>
+          <t>175814</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>286524</t>
+          <t>284599</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>346716</t>
+          <t>345689</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,59%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42166</t>
+          <t>40718</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71488</t>
+          <t>71611</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49489</t>
+          <t>48183</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78890</t>
+          <t>78080</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>98412</t>
+          <t>97737</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>138651</t>
+          <t>139912</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48955</t>
+          <t>47724</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>80935</t>
+          <t>78788</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>75017</t>
+          <t>74960</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>108767</t>
+          <t>108762</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>132049</t>
+          <t>131816</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>180717</t>
+          <t>178474</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58371</t>
+          <t>58346</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>90345</t>
+          <t>91880</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48827</t>
+          <t>47376</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>78166</t>
+          <t>76858</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>113637</t>
+          <t>111019</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>157810</t>
+          <t>156514</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>123458</t>
+          <t>120814</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>165371</t>
+          <t>166594</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>152362</t>
+          <t>152172</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>198657</t>
+          <t>197194</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>286541</t>
+          <t>285701</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>347432</t>
+          <t>349674</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,78%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>134237</t>
+          <t>132931</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>175964</t>
+          <t>176934</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>143691</t>
+          <t>144184</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>187230</t>
+          <t>187930</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>287569</t>
+          <t>289130</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>348522</t>
+          <t>350761</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,88%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52865</t>
+          <t>51487</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>86076</t>
+          <t>84353</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>63464</t>
+          <t>62788</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>95998</t>
+          <t>97499</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>124584</t>
+          <t>123878</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>169823</t>
+          <t>171284</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>76014</t>
+          <t>75513</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>112635</t>
+          <t>113541</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>73981</t>
+          <t>71700</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>107193</t>
+          <t>107928</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>158201</t>
+          <t>159968</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>208325</t>
+          <t>212558</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,32%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>30967</t>
+          <t>31253</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>56768</t>
+          <t>57796</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>16160</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>36422</t>
+          <t>37457</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>51619</t>
+          <t>52758</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>86460</t>
+          <t>86106</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>83079</t>
+          <t>85659</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>122018</t>
+          <t>121238</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>88038</t>
+          <t>87947</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>125532</t>
+          <t>125854</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>182923</t>
+          <t>181233</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>235329</t>
+          <t>232999</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,3%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>107761</t>
+          <t>104915</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>147150</t>
+          <t>146338</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>115610</t>
+          <t>114723</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>156952</t>
+          <t>156506</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>234961</t>
+          <t>236169</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>291434</t>
+          <t>293759</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,16%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>57900</t>
+          <t>56820</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>91624</t>
+          <t>89446</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>58873</t>
+          <t>59207</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>92899</t>
+          <t>94039</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>125446</t>
+          <t>126720</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>172487</t>
+          <t>171449</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,35%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>72414</t>
+          <t>73159</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>107815</t>
+          <t>109027</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>92786</t>
+          <t>92801</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>130225</t>
+          <t>131839</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>176904</t>
+          <t>174280</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>228981</t>
+          <t>227589</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,69%</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>6682</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>22300</t>
+          <t>22130</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4122</t>
+          <t>4217</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>17051</t>
+          <t>17576</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>13710</t>
+          <t>13839</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>33413</t>
+          <t>33784</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>53161</t>
+          <t>54243</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>83784</t>
+          <t>82923</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>38757</t>
+          <t>39174</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>65929</t>
+          <t>67222</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>101515</t>
+          <t>100822</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>142083</t>
+          <t>140415</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,53%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>77966</t>
+          <t>78081</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>112005</t>
+          <t>109362</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>110619</t>
+          <t>110562</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>147289</t>
+          <t>146432</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>197327</t>
+          <t>197023</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>246987</t>
+          <t>246063</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>35,98%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>48719</t>
+          <t>48879</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>78739</t>
+          <t>76781</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>58775</t>
+          <t>60044</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>92385</t>
+          <t>91444</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>115748</t>
+          <t>115063</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>157913</t>
+          <t>158149</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,13%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>68892</t>
+          <t>70464</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>101307</t>
+          <t>101553</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>83362</t>
+          <t>83030</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>117773</t>
+          <t>118607</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>164324</t>
+          <t>161627</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>211176</t>
+          <t>209169</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,59%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>11604</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>3474</t>
+          <t>2786</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>15984</t>
+          <t>15863</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>8346</t>
+          <t>8530</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>25255</t>
+          <t>24650</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>20894</t>
+          <t>20335</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>37871</t>
+          <t>39209</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>44524</t>
+          <t>44393</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>74862</t>
+          <t>77024</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>70420</t>
+          <t>70364</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>107827</t>
+          <t>108510</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,31%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>60185</t>
+          <t>61230</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>87196</t>
+          <t>87317</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>101131</t>
+          <t>100832</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>141819</t>
+          <t>143182</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>171911</t>
+          <t>170694</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>221312</t>
+          <t>221146</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,28%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>51262</t>
+          <t>49345</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>75581</t>
+          <t>74439</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>53632</t>
+          <t>54665</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>89666</t>
+          <t>87342</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>111157</t>
+          <t>112856</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>156885</t>
+          <t>153465</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,49%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>59470</t>
+          <t>58880</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>85086</t>
+          <t>85161</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>102603</t>
+          <t>105968</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>146032</t>
+          <t>148167</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>173344</t>
+          <t>174494</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>220018</t>
+          <t>223663</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,69%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>279654</t>
+          <t>278571</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>348754</t>
+          <t>346149</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>221359</t>
+          <t>223808</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>283908</t>
+          <t>282967</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>521810</t>
+          <t>521245</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>612555</t>
+          <t>610434</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>680428</t>
+          <t>680430</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>773753</t>
+          <t>772857</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5638,7 +5638,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>732802</t>
+          <t>731722</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>830799</t>
+          <t>828586</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1438837</t>
+          <t>1439271</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1572458</t>
+          <t>1573771</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,87%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>720362</t>
+          <t>722238</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>815338</t>
+          <t>820541</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>865861</t>
+          <t>864666</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>964915</t>
+          <t>961592</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1613853</t>
+          <t>1615897</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1752680</t>
+          <t>1762044</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,21%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>330688</t>
+          <t>328465</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>404019</t>
+          <t>399353</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>389115</t>
+          <t>393375</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>470399</t>
+          <t>470133</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>740085</t>
+          <t>744716</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>846161</t>
+          <t>851703</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>432030</t>
+          <t>427808</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>510298</t>
+          <t>510365</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>585361</t>
+          <t>585189</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>677930</t>
+          <t>673185</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1040577</t>
+          <t>1038781</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1165572</t>
+          <t>1163154</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -6417,32 +6417,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>32626</t>
+          <t>32378</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18570</t>
+          <t>19687</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52091</t>
+          <t>50618</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6452,32 +6452,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>27986</t>
+          <t>28376</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18090</t>
+          <t>18803</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43134</t>
+          <t>43932</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6487,32 +6487,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>60611</t>
+          <t>60754</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42752</t>
+          <t>42314</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86036</t>
+          <t>81352</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -6530,32 +6530,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>64290</t>
+          <t>63252</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42982</t>
+          <t>43203</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90111</t>
+          <t>82515</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6565,32 +6565,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>42574</t>
+          <t>51076</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28770</t>
+          <t>36574</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60265</t>
+          <t>69304</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6600,32 +6600,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>106863</t>
+          <t>114328</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>79062</t>
+          <t>88938</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>136509</t>
+          <t>140626</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,72%</t>
         </is>
       </c>
     </row>
@@ -6643,32 +6643,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>57781</t>
+          <t>46542</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37518</t>
+          <t>29764</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>85258</t>
+          <t>67655</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6678,32 +6678,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>46072</t>
+          <t>51216</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31486</t>
+          <t>36142</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61651</t>
+          <t>71200</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6713,32 +6713,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>103854</t>
+          <t>97757</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>78072</t>
+          <t>76602</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>133946</t>
+          <t>124856</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>32,6%</t>
         </is>
       </c>
     </row>
@@ -6756,32 +6756,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22227</t>
+          <t>19947</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9632</t>
+          <t>9152</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43812</t>
+          <t>39840</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6791,32 +6791,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20554</t>
+          <t>22564</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10847</t>
+          <t>12006</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35088</t>
+          <t>36146</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6826,32 +6826,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>42782</t>
+          <t>42510</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26655</t>
+          <t>25640</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66433</t>
+          <t>63082</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -6869,32 +6869,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>11979</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>4564</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21168</t>
+          <t>24601</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6904,32 +6904,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>48581</t>
+          <t>55630</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33987</t>
+          <t>38568</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>67220</t>
+          <t>74613</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6939,32 +6939,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>58062</t>
+          <t>67609</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40640</t>
+          <t>48298</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>80013</t>
+          <t>91320</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>23,85%</t>
         </is>
       </c>
     </row>
@@ -6982,17 +6982,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>186405</t>
+          <t>174098</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>186405</t>
+          <t>174098</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>186405</t>
+          <t>174098</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7017,17 +7017,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>185767</t>
+          <t>208862</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>185767</t>
+          <t>208862</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>185767</t>
+          <t>208862</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7052,17 +7052,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>372172</t>
+          <t>382960</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>372172</t>
+          <t>382960</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>372172</t>
+          <t>382960</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7099,32 +7099,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>32792</t>
+          <t>38467</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21363</t>
+          <t>25612</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49217</t>
+          <t>52620</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7134,32 +7134,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>37861</t>
+          <t>40955</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26488</t>
+          <t>29155</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52245</t>
+          <t>55063</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7169,32 +7169,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>70653</t>
+          <t>79422</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54218</t>
+          <t>61641</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89654</t>
+          <t>101568</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -7212,32 +7212,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>104889</t>
+          <t>111321</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85634</t>
+          <t>89602</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>125386</t>
+          <t>133621</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7247,32 +7247,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>108637</t>
+          <t>121699</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>90073</t>
+          <t>101612</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>127081</t>
+          <t>139612</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7282,32 +7282,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>213526</t>
+          <t>233020</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>186785</t>
+          <t>203596</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>240566</t>
+          <t>262537</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>38,9%</t>
         </is>
       </c>
     </row>
@@ -7325,32 +7325,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>77758</t>
+          <t>91882</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>59107</t>
+          <t>72140</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>97173</t>
+          <t>113591</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7360,32 +7360,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>88842</t>
+          <t>100661</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>73772</t>
+          <t>84980</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>107638</t>
+          <t>119747</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7395,32 +7395,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>166600</t>
+          <t>192543</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>142480</t>
+          <t>167316</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>191343</t>
+          <t>221573</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>32,83%</t>
         </is>
       </c>
     </row>
@@ -7438,32 +7438,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28914</t>
+          <t>31621</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17800</t>
+          <t>18860</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44893</t>
+          <t>48282</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7473,32 +7473,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>42188</t>
+          <t>47461</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30958</t>
+          <t>34171</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55703</t>
+          <t>62484</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7508,32 +7508,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>71102</t>
+          <t>79082</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54254</t>
+          <t>61764</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89886</t>
+          <t>100029</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -7551,32 +7551,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>26578</t>
+          <t>25823</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15930</t>
+          <t>16609</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41802</t>
+          <t>42283</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7586,32 +7586,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>60507</t>
+          <t>65092</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>46088</t>
+          <t>51795</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76555</t>
+          <t>81459</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7621,32 +7621,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>87085</t>
+          <t>90915</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>68593</t>
+          <t>72467</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>108368</t>
+          <t>110325</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -7664,17 +7664,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>270931</t>
+          <t>299115</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>270931</t>
+          <t>299115</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>270931</t>
+          <t>299115</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7699,17 +7699,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>338035</t>
+          <t>375867</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>338035</t>
+          <t>375867</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>338035</t>
+          <t>375867</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7734,17 +7734,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>608966</t>
+          <t>674982</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>608966</t>
+          <t>674982</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>608966</t>
+          <t>674982</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>45601</t>
+          <t>52430</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33405</t>
+          <t>39119</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61262</t>
+          <t>66947</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7816,32 +7816,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>45283</t>
+          <t>51058</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35960</t>
+          <t>40588</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56785</t>
+          <t>63813</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7851,32 +7851,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>90885</t>
+          <t>103488</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>75361</t>
+          <t>87951</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>109350</t>
+          <t>123274</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -7894,32 +7894,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>123896</t>
+          <t>147617</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>106192</t>
+          <t>127746</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>144260</t>
+          <t>168586</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7929,32 +7929,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>137582</t>
+          <t>155785</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>122714</t>
+          <t>139564</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>152766</t>
+          <t>174017</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7964,32 +7964,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>261478</t>
+          <t>303402</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>237030</t>
+          <t>277910</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>287914</t>
+          <t>331264</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,59%</t>
         </is>
       </c>
     </row>
@@ -8007,32 +8007,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>126526</t>
+          <t>136156</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>108582</t>
+          <t>117383</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>146771</t>
+          <t>159388</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8042,32 +8042,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>129388</t>
+          <t>147528</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>114378</t>
+          <t>131255</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>145912</t>
+          <t>163281</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8077,32 +8077,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>255913</t>
+          <t>283684</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>231373</t>
+          <t>256249</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>280693</t>
+          <t>310534</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>31,49%</t>
         </is>
       </c>
     </row>
@@ -8120,32 +8120,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>59123</t>
+          <t>64142</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46102</t>
+          <t>50314</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74715</t>
+          <t>79945</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8155,32 +8155,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>56010</t>
+          <t>64792</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45510</t>
+          <t>53231</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68722</t>
+          <t>78628</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8190,32 +8190,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>115133</t>
+          <t>128934</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>98842</t>
+          <t>108475</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>134636</t>
+          <t>149068</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -8233,22 +8233,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>57889</t>
+          <t>63313</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>44469</t>
+          <t>49957</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>74634</t>
+          <t>81796</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8268,32 +8268,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>89096</t>
+          <t>103301</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>76378</t>
+          <t>89240</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>102619</t>
+          <t>119741</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8303,32 +8303,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>146986</t>
+          <t>166614</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>128432</t>
+          <t>145141</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>169116</t>
+          <t>188672</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -8346,17 +8346,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>413035</t>
+          <t>463658</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>413035</t>
+          <t>463658</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>413035</t>
+          <t>463658</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8381,17 +8381,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>457360</t>
+          <t>522464</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>457360</t>
+          <t>522464</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>457360</t>
+          <t>522464</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8416,17 +8416,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>870395</t>
+          <t>986122</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>870395</t>
+          <t>986122</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>870395</t>
+          <t>986122</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8463,32 +8463,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>39851</t>
+          <t>48784</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28701</t>
+          <t>35805</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53082</t>
+          <t>65039</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8498,27 +8498,27 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>43190</t>
+          <t>45301</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32517</t>
+          <t>35840</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55134</t>
+          <t>56681</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -8533,32 +8533,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>83041</t>
+          <t>94085</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>66900</t>
+          <t>77081</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>100996</t>
+          <t>112955</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -8576,32 +8576,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>145403</t>
+          <t>161960</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>125615</t>
+          <t>139523</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>167858</t>
+          <t>183586</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8611,32 +8611,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>167484</t>
+          <t>180326</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>136315</t>
+          <t>162886</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>186852</t>
+          <t>200348</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8646,32 +8646,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>312887</t>
+          <t>342286</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>279174</t>
+          <t>313385</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>342200</t>
+          <t>370734</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -8689,32 +8689,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>173398</t>
+          <t>183569</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>150874</t>
+          <t>158750</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>194090</t>
+          <t>207185</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8724,32 +8724,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>216804</t>
+          <t>201211</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>186740</t>
+          <t>182064</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>306086</t>
+          <t>220037</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8759,32 +8759,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>390201</t>
+          <t>384780</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>352998</t>
+          <t>357064</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>473788</t>
+          <t>414899</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>32,99%</t>
         </is>
       </c>
     </row>
@@ -8802,32 +8802,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>70581</t>
+          <t>78631</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>54944</t>
+          <t>64111</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>87059</t>
+          <t>99577</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8837,32 +8837,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>86202</t>
+          <t>95458</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>69034</t>
+          <t>81190</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>100393</t>
+          <t>110690</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8872,32 +8872,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>156784</t>
+          <t>174089</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>135018</t>
+          <t>153473</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>178563</t>
+          <t>197756</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -8915,32 +8915,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>115103</t>
+          <t>122565</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>98200</t>
+          <t>104360</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>136379</t>
+          <t>144681</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8950,32 +8950,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>130118</t>
+          <t>139897</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>108150</t>
+          <t>124482</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>148801</t>
+          <t>158397</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8985,32 +8985,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>245221</t>
+          <t>262462</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>213876</t>
+          <t>234998</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>271231</t>
+          <t>286137</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -9028,17 +9028,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>544337</t>
+          <t>595508</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>544337</t>
+          <t>595508</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>544337</t>
+          <t>595508</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9063,17 +9063,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>643798</t>
+          <t>662194</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>643798</t>
+          <t>662194</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>643798</t>
+          <t>662194</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9098,17 +9098,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1188134</t>
+          <t>1257702</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1188134</t>
+          <t>1257702</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1188134</t>
+          <t>1257702</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9145,32 +9145,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>44989</t>
+          <t>50086</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>33764</t>
+          <t>36941</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>59014</t>
+          <t>65758</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9180,32 +9180,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>30732</t>
+          <t>34518</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>22759</t>
+          <t>26469</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>38908</t>
+          <t>43888</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9215,32 +9215,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>75721</t>
+          <t>84604</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>62752</t>
+          <t>68248</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>93893</t>
+          <t>101668</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -9258,32 +9258,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>123318</t>
+          <t>130532</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>106024</t>
+          <t>112369</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>143937</t>
+          <t>149384</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9293,32 +9293,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>104043</t>
+          <t>117191</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>90625</t>
+          <t>103092</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>118135</t>
+          <t>133039</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9328,32 +9328,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>227361</t>
+          <t>247722</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>206207</t>
+          <t>226140</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>251857</t>
+          <t>272686</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -9371,32 +9371,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>140822</t>
+          <t>153046</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>122171</t>
+          <t>132929</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>157638</t>
+          <t>174717</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9406,32 +9406,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>158980</t>
+          <t>175074</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>143154</t>
+          <t>157114</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>173864</t>
+          <t>192937</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9441,32 +9441,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>299802</t>
+          <t>328120</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>277531</t>
+          <t>301985</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>323704</t>
+          <t>355511</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,7%</t>
         </is>
       </c>
     </row>
@@ -9484,102 +9484,102 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>97170</t>
+          <t>104498</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>81458</t>
+          <t>87401</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>114448</t>
+          <t>123728</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
+          <t>18,98%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>15,87%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>22,47%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>108164</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>93604</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>122635</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>18,95%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>16,4%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>21,49%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>212662</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>191446</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>235591</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
           <t>18,96%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>15,9%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>22,34%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>97167</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>84859</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>110715</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>18,99%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>16,58%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>21,63%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>194337</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>174632</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>214395</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>18,97%</t>
-        </is>
-      </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -9597,32 +9597,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>106080</t>
+          <t>112458</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>90452</t>
+          <t>95427</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>126054</t>
+          <t>131580</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9632,32 +9632,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>120888</t>
+          <t>135796</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>108031</t>
+          <t>121105</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>135452</t>
+          <t>151516</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>226968</t>
+          <t>248255</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>205271</t>
+          <t>223870</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>249910</t>
+          <t>272074</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,26%</t>
         </is>
       </c>
     </row>
@@ -9710,17 +9710,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>512379</t>
+          <t>550620</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>512379</t>
+          <t>550620</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>512379</t>
+          <t>550620</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -9745,17 +9745,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>511811</t>
+          <t>570743</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>511811</t>
+          <t>570743</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>511811</t>
+          <t>570743</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -9780,17 +9780,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1024190</t>
+          <t>1121363</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1024190</t>
+          <t>1121363</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1024190</t>
+          <t>1121363</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -9827,32 +9827,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>15157</t>
+          <t>16892</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>10812</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>22287</t>
+          <t>24737</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9862,32 +9862,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>14516</t>
+          <t>14995</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4860</t>
+          <t>9842</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25594</t>
+          <t>20591</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9897,32 +9897,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>29673</t>
+          <t>31888</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>13841</t>
+          <t>23968</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>42532</t>
+          <t>41827</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -9940,32 +9940,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>64292</t>
+          <t>69527</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>53392</t>
+          <t>57385</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>77451</t>
+          <t>83662</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9975,32 +9975,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>79349</t>
+          <t>85445</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>29504</t>
+          <t>73649</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>126247</t>
+          <t>97632</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10010,32 +10010,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>143641</t>
+          <t>154972</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>69970</t>
+          <t>136407</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>189980</t>
+          <t>172753</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -10053,32 +10053,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>104177</t>
+          <t>114803</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>90850</t>
+          <t>99464</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>118198</t>
+          <t>130119</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10088,32 +10088,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>335685</t>
+          <t>141015</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>194230</t>
+          <t>127577</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>497759</t>
+          <t>155466</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>439862</t>
+          <t>255818</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>293629</t>
+          <t>237425</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>705212</t>
+          <t>278355</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>34,54%</t>
         </is>
       </c>
     </row>
@@ -10166,32 +10166,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>69070</t>
+          <t>78291</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>58047</t>
+          <t>65780</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>82816</t>
+          <t>92054</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10201,32 +10201,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>68211</t>
+          <t>74716</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>25054</t>
+          <t>64219</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>108081</t>
+          <t>85603</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>137281</t>
+          <t>153007</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>66383</t>
+          <t>136624</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>181483</t>
+          <t>171406</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -10279,32 +10279,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>95709</t>
+          <t>104679</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>82289</t>
+          <t>90172</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>109790</t>
+          <t>118911</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -10314,32 +10314,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>95668</t>
+          <t>105630</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>34538</t>
+          <t>93521</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>152631</t>
+          <t>118397</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>191377</t>
+          <t>210309</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>86988</t>
+          <t>190226</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>251682</t>
+          <t>229095</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>28,42%</t>
         </is>
       </c>
     </row>
@@ -10392,17 +10392,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>348405</t>
+          <t>384193</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>348405</t>
+          <t>384193</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>348405</t>
+          <t>384193</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -10427,17 +10427,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>593429</t>
+          <t>421801</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>593429</t>
+          <t>421801</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>593429</t>
+          <t>421801</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>941834</t>
+          <t>805994</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>941834</t>
+          <t>805994</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>941834</t>
+          <t>805994</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -10509,32 +10509,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>8435</t>
+          <t>9004</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>4592</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>14218</t>
+          <t>15316</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10544,32 +10544,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>15114</t>
+          <t>16235</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>9956</t>
+          <t>10790</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>21165</t>
+          <t>23642</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10579,32 +10579,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>23549</t>
+          <t>25240</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>16534</t>
+          <t>17878</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>31371</t>
+          <t>33264</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -10622,32 +10622,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>42782</t>
+          <t>47102</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>33909</t>
+          <t>37061</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>52736</t>
+          <t>57881</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10657,32 +10657,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>60099</t>
+          <t>64157</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>50298</t>
+          <t>53635</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>72056</t>
+          <t>76435</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10692,32 +10692,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>102881</t>
+          <t>111259</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>91008</t>
+          <t>95405</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>118232</t>
+          <t>125964</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -10735,32 +10735,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>74409</t>
+          <t>82089</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>64142</t>
+          <t>70222</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>85860</t>
+          <t>94320</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10770,32 +10770,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>108459</t>
+          <t>117939</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>96361</t>
+          <t>104530</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>121237</t>
+          <t>131139</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10805,32 +10805,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>182869</t>
+          <t>200029</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>165894</t>
+          <t>181569</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>201689</t>
+          <t>219562</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,63%</t>
         </is>
       </c>
     </row>
@@ -10848,32 +10848,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>78580</t>
+          <t>85507</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>66424</t>
+          <t>72989</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>90673</t>
+          <t>99130</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10883,32 +10883,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>100877</t>
+          <t>111056</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>89509</t>
+          <t>98410</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>113268</t>
+          <t>125438</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10918,32 +10918,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>179457</t>
+          <t>196563</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>163080</t>
+          <t>179019</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>196585</t>
+          <t>215008</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,02%</t>
         </is>
       </c>
     </row>
@@ -10961,32 +10961,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>72585</t>
+          <t>79039</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>61995</t>
+          <t>67411</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>85994</t>
+          <t>91848</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10996,32 +10996,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>118193</t>
+          <t>128851</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>105330</t>
+          <t>115455</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>130981</t>
+          <t>143309</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11031,32 +11031,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>190779</t>
+          <t>207890</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>172087</t>
+          <t>191108</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>207727</t>
+          <t>229050</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,91%</t>
         </is>
       </c>
     </row>
@@ -11074,17 +11074,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>276791</t>
+          <t>302741</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>276791</t>
+          <t>302741</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>276791</t>
+          <t>302741</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -11109,17 +11109,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>402743</t>
+          <t>438238</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>402743</t>
+          <t>438238</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>402743</t>
+          <t>438238</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -11144,17 +11144,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>679534</t>
+          <t>740980</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>679534</t>
+          <t>740980</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>679534</t>
+          <t>740980</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -11191,32 +11191,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>219452</t>
+          <t>248042</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>189985</t>
+          <t>213635</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>253249</t>
+          <t>282025</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11226,32 +11226,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>214681</t>
+          <t>231439</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>169140</t>
+          <t>206786</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>245341</t>
+          <t>258619</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11261,32 +11261,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>434133</t>
+          <t>479481</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>376305</t>
+          <t>439419</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>477555</t>
+          <t>525776</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -11304,32 +11304,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>668869</t>
+          <t>731310</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>624114</t>
+          <t>688161</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>719194</t>
+          <t>781603</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11339,32 +11339,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>699768</t>
+          <t>775679</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>514877</t>
+          <t>734943</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>764924</t>
+          <t>822304</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11374,32 +11374,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>1368637</t>
+          <t>1506990</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1198206</t>
+          <t>1439289</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1452035</t>
+          <t>1574921</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -11417,32 +11417,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>754872</t>
+          <t>808088</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>709204</t>
+          <t>758096</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>807642</t>
+          <t>858923</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11452,32 +11452,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>1084229</t>
+          <t>934644</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>917760</t>
+          <t>890895</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1561249</t>
+          <t>977844</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11487,32 +11487,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>1839101</t>
+          <t>1742732</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1666576</t>
+          <t>1678391</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>2360790</t>
+          <t>1814012</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>30,38%</t>
         </is>
       </c>
     </row>
@@ -11530,22 +11530,22 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>425664</t>
+          <t>462637</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>388860</t>
+          <t>422086</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>465000</t>
+          <t>507319</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -11555,7 +11555,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11565,32 +11565,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>471211</t>
+          <t>524211</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>371900</t>
+          <t>491429</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>521615</t>
+          <t>561460</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11600,32 +11600,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>896876</t>
+          <t>986847</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>794632</t>
+          <t>937906</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>966083</t>
+          <t>1043420</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -11643,32 +11643,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>483425</t>
+          <t>519857</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>443283</t>
+          <t>477579</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>522492</t>
+          <t>562589</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11678,32 +11678,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>663053</t>
+          <t>734196</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>527623</t>
+          <t>691994</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>726740</t>
+          <t>772919</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -11713,32 +11713,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>1146478</t>
+          <t>1254053</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1002787</t>
+          <t>1199179</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1217733</t>
+          <t>1316351</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -11756,17 +11756,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>2552282</t>
+          <t>2769934</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>2552282</t>
+          <t>2769934</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2552282</t>
+          <t>2769934</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -11791,17 +11791,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>3132942</t>
+          <t>3200169</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>3132942</t>
+          <t>3200169</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3132942</t>
+          <t>3200169</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -11826,17 +11826,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>5685225</t>
+          <t>5970103</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>5685225</t>
+          <t>5970103</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>5685225</t>
+          <t>5970103</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
